--- a/多音字.xlsx
+++ b/多音字.xlsx
@@ -33,7 +33,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="439" uniqueCount="391">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="444" uniqueCount="394">
   <si>
     <t>日</t>
   </si>
@@ -1359,6 +1359,15 @@
     <t>合理｜ごうり、連合｜れんごう</t>
   </si>
   <si>
+    <t>無</t>
+  </si>
+  <si>
+    <t>無用｜むよう</t>
+  </si>
+  <si>
+    <t>無礼｜ぶれい</t>
+  </si>
+  <si>
     <t>田</t>
   </si>
 </sst>
@@ -1372,7 +1381,7 @@
     <numFmt numFmtId="176" formatCode="_ * #,##0.00_ ;_ * \-#,##0.00_ ;_ * &quot;-&quot;??_ ;_ @_ "/>
     <numFmt numFmtId="177" formatCode="_ * #,##0_ ;_ * \-#,##0_ ;_ * &quot;-&quot;_ ;_ @_ "/>
   </numFmts>
-  <fonts count="29">
+  <fonts count="28">
     <font>
       <sz val="11"/>
       <color theme="1"/>
@@ -1421,13 +1430,6 @@
       <color theme="1"/>
       <name val="等线"/>
       <charset val="134"/>
-    </font>
-    <font>
-      <sz val="11"/>
-      <color theme="1"/>
-      <name val="等线"/>
-      <charset val="134"/>
-      <scheme val="minor"/>
     </font>
     <font>
       <u/>
@@ -1883,148 +1885,148 @@
   </borders>
   <cellStyleXfs count="49">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
-    <xf numFmtId="176" fontId="8" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="44" fontId="8" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="9" fontId="8" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="177" fontId="8" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="42" fontId="8" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="176" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="44" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="9" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="177" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="42" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="8" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="9" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
+    <xf numFmtId="0" fontId="0" fillId="2" borderId="1" applyNumberFormat="0" applyFont="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
     <xf numFmtId="0" fontId="10" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="8" fillId="2" borderId="1" applyNumberFormat="0" applyFont="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
     <xf numFmtId="0" fontId="11" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="12" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="13" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="13" fillId="0" borderId="2" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="14" fillId="0" borderId="2" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="15" fillId="0" borderId="2" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="16" fillId="0" borderId="3" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="16" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="17" fillId="3" borderId="4" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="18" fillId="4" borderId="5" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="19" fillId="4" borderId="4" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="20" fillId="5" borderId="6" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="21" fillId="0" borderId="7" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="22" fillId="0" borderId="8" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="23" fillId="6" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="24" fillId="7" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="25" fillId="8" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="26" fillId="9" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="27" fillId="10" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="27" fillId="11" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="26" fillId="12" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="26" fillId="13" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="27" fillId="14" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="27" fillId="15" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="26" fillId="16" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="26" fillId="17" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="27" fillId="18" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="27" fillId="19" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="26" fillId="20" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="26" fillId="21" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="27" fillId="22" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="27" fillId="23" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="26" fillId="24" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="26" fillId="25" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="27" fillId="26" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="27" fillId="27" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="26" fillId="28" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="26" fillId="29" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="27" fillId="30" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="27" fillId="31" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="26" fillId="32" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="15" fillId="0" borderId="3" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="15" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="16" fillId="3" borderId="4" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="17" fillId="4" borderId="5" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="18" fillId="4" borderId="4" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="19" fillId="5" borderId="6" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="20" fillId="0" borderId="7" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="21" fillId="0" borderId="8" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="22" fillId="6" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="23" fillId="7" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="24" fillId="8" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="25" fillId="9" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="26" fillId="10" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="26" fillId="11" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="25" fillId="12" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="25" fillId="13" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="26" fillId="14" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="26" fillId="15" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="25" fillId="16" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="25" fillId="17" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="26" fillId="18" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="26" fillId="19" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="25" fillId="20" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="25" fillId="21" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="26" fillId="22" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="26" fillId="23" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="25" fillId="24" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="25" fillId="25" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="26" fillId="26" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="26" fillId="27" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="25" fillId="28" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="25" fillId="29" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="26" fillId="30" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="26" fillId="31" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="25" fillId="32" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
   </cellStyleXfs>
@@ -2368,7 +2370,7 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData">
   <sheetPr/>
-  <dimension ref="A2:E268"/>
+  <dimension ref="A2:E271"/>
   <sheetFormatPr defaultColWidth="9" defaultRowHeight="13.8" outlineLevelCol="4"/>
   <cols>
     <col min="3" max="3" width="47.5555555555556" customWidth="1"/>
@@ -4077,6 +4079,25 @@
       </c>
       <c r="C268" t="s">
         <v>389</v>
+      </c>
+    </row>
+    <row r="270" spans="1:3">
+      <c r="A270" t="s">
+        <v>390</v>
+      </c>
+      <c r="B270" t="s">
+        <v>326</v>
+      </c>
+      <c r="C270" t="s">
+        <v>391</v>
+      </c>
+    </row>
+    <row r="271" spans="1:3">
+      <c r="B271" t="s">
+        <v>189</v>
+      </c>
+      <c r="C271" t="s">
+        <v>392</v>
       </c>
     </row>
   </sheetData>
@@ -4093,7 +4114,7 @@
   <sheetData>
     <row r="2" spans="1:1">
       <c r="A2" t="s">
-        <v>390</v>
+        <v>393</v>
       </c>
     </row>
   </sheetData>
